--- a/AAAGameData/DataTables/Story/StoryTriggerTable.xlsx
+++ b/AAAGameData/DataTables/Story/StoryTriggerTable.xlsx
@@ -121,7 +121,7 @@
     <t>LTest clear</t>
   </si>
   <si>
-    <t>Lv_Test</t>
+    <t>LvTest</t>
   </si>
   <si>
     <t>Story_LTest</t>
